--- a/ValueSet-ACCESSReportTypeVS.xlsx
+++ b/ValueSet-ACCESSReportTypeVS.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.6</t>
+    <t>0.9.8</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T13:45:33-04:00</t>
+    <t>2026-05-18T15:59:44-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-ACCESSReportTypeVS.xlsx
+++ b/ValueSet-ACCESSReportTypeVS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-18T15:59:44-04:00</t>
+    <t>2026-05-20T09:30:43-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-ACCESSReportTypeVS.xlsx
+++ b/ValueSet-ACCESSReportTypeVS.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.8</t>
+    <t>0.9.11</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-20T09:30:43-04:00</t>
+    <t>2026-06-04T22:54:52-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-ACCESSReportTypeVS.xlsx
+++ b/ValueSet-ACCESSReportTypeVS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-04T22:54:52-04:00</t>
+    <t>2026-06-04T23:05:21-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-ACCESSReportTypeVS.xlsx
+++ b/ValueSet-ACCESSReportTypeVS.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.11</t>
+    <t>0.9.12</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-04T23:05:21-04:00</t>
+    <t>2026-06-10T23:08:55-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
